--- a/All data/results_publication_summary.xlsx
+++ b/All data/results_publication_summary.xlsx
@@ -5,29 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/44e2464d2a9165ff/Postdoc/2024 Plastic-detection/Plastic_tracker_codes/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/44e2464d2a9165ff/Postdoc/2024 Plastic-detection/Plastic_tracker_codes/writing/submissions SciAdv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="11_6DFD1F569141DE0E62355476585DCE3A8745CDEE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28B53569-D69A-40CE-815E-A248B9FBD1D6}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{FABD14B2-83CE-49FE-812C-ED495E223DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C92241C8-D59C-42FB-A0A6-EF7CA2ACD66A}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -36,65 +25,50 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>Common name</t>
   </si>
   <si>
-    <t>w (cm/s)_mean</t>
-  </si>
-  <si>
-    <t>w (cm/s)_p10</t>
-  </si>
-  <si>
-    <t>w (cm/s)_p90</t>
-  </si>
-  <si>
-    <t>v (cm/s)_mean</t>
-  </si>
-  <si>
-    <t>v (cm/s)_p10</t>
-  </si>
-  <si>
-    <t>v (cm/s)_p90</t>
-  </si>
-  <si>
-    <t>drift (cm)_mean</t>
-  </si>
-  <si>
-    <t>drift (cm)_p10</t>
-  </si>
-  <si>
-    <t>drift (cm)_p90</t>
-  </si>
-  <si>
-    <t>drift_gradient (-)_mean</t>
-  </si>
-  <si>
-    <t>drift_gradient (-)_p10</t>
-  </si>
-  <si>
-    <t>drift_gradient (-)_p90</t>
-  </si>
-  <si>
-    <t>amplitude (-)_mean</t>
-  </si>
-  <si>
-    <t>amplitude (-)_p10</t>
-  </si>
-  <si>
-    <t>amplitude (-)_p90</t>
-  </si>
-  <si>
-    <t>dominant_mode_most_common</t>
+    <t>vz_mean_mean</t>
+  </si>
+  <si>
+    <t>vz_mean_median</t>
+  </si>
+  <si>
+    <t>vz_mean_p10</t>
+  </si>
+  <si>
+    <t>vz_mean_p90</t>
+  </si>
+  <si>
+    <t>Re_mean</t>
+  </si>
+  <si>
+    <t>Re_median</t>
+  </si>
+  <si>
+    <t>Re_p10</t>
+  </si>
+  <si>
+    <t>Re_p90</t>
+  </si>
+  <si>
+    <t>Cd_mean</t>
+  </si>
+  <si>
+    <t>Cd_median</t>
+  </si>
+  <si>
+    <t>Cd_p10</t>
+  </si>
+  <si>
+    <t>Cd_p90</t>
   </si>
   <si>
     <t>Beverage bottles &lt; 0.5 litre</t>
   </si>
   <si>
-    <t>Straight oblique</t>
-  </si>
-  <si>
     <t>Beverage bottles &gt; 0.5 litre</t>
   </si>
   <si>
@@ -104,33 +78,21 @@
     <t>Candy, snack and crisps packaging</t>
   </si>
   <si>
-    <t>Nonlinear oblique</t>
-  </si>
-  <si>
     <t>Cigarette filters</t>
   </si>
   <si>
-    <t>Nonlinear vertical</t>
-  </si>
-  <si>
     <t>Cotton swab</t>
   </si>
   <si>
     <t>Foam plastic pieces 0.5-2.5 cm</t>
   </si>
   <si>
-    <t>Mixed</t>
-  </si>
-  <si>
     <t>Foam plastic pieces 2.5-50 cm</t>
   </si>
   <si>
     <t>Glass bottle caps (e.g., beer caps)</t>
   </si>
   <si>
-    <t>Straight vertical</t>
-  </si>
-  <si>
     <t>Glass bottles, jars and fragments</t>
   </si>
   <si>
@@ -174,9 +136,6 @@
   </si>
   <si>
     <t>Wet wipes</t>
-  </si>
-  <si>
-    <t>Count</t>
   </si>
 </sst>
 </file>
@@ -539,89 +498,66 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="13" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>17</v>
-      </c>
       <c r="B2">
-        <v>44</v>
+        <v>8.4702712528530419</v>
       </c>
       <c r="C2">
-        <v>8.4702712528530419</v>
+        <v>8.0731750085462046</v>
       </c>
       <c r="D2">
         <v>6.776507707201703</v>
@@ -630,54 +566,39 @@
         <v>11.06157761859337</v>
       </c>
       <c r="F2">
-        <v>2.98252596502895</v>
+        <v>11118.37932560081</v>
       </c>
       <c r="G2">
-        <v>1.0223700991896969</v>
+        <v>10978.18260376742</v>
       </c>
       <c r="H2">
-        <v>5.2757064904113662</v>
+        <v>8496.4375954008101</v>
       </c>
       <c r="I2">
-        <v>12.38491851424946</v>
+        <v>13385.929503424401</v>
       </c>
       <c r="J2">
-        <v>4.5895278565856001</v>
+        <v>1.7352808337928121</v>
       </c>
       <c r="K2">
-        <v>19.49431074362078</v>
+        <v>1.588500218817086</v>
       </c>
       <c r="L2">
-        <v>0.35858825058154242</v>
+        <v>0.87973490337816085</v>
       </c>
       <c r="M2">
-        <v>0.1179023152759818</v>
-      </c>
-      <c r="N2">
-        <v>0.56791184701790487</v>
-      </c>
-      <c r="O2">
-        <v>0.64554641908438171</v>
-      </c>
-      <c r="P2">
-        <v>0.20599063003563561</v>
-      </c>
-      <c r="Q2">
-        <v>1.3971062306740061</v>
-      </c>
-      <c r="R2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+        <v>2.306799862533087</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B3">
-        <v>45</v>
+        <v>8.3186142931652558</v>
       </c>
       <c r="C3">
-        <v>8.3186142931652558</v>
+        <v>8.0566697613181066</v>
       </c>
       <c r="D3">
         <v>5.6798396837369038</v>
@@ -686,54 +607,39 @@
         <v>11.50627885145264</v>
       </c>
       <c r="F3">
-        <v>2.3283863450077158</v>
+        <v>14604.93848717873</v>
       </c>
       <c r="G3">
-        <v>0.46410224243559878</v>
+        <v>14986.794580289879</v>
       </c>
       <c r="H3">
-        <v>4.2152351166254096</v>
+        <v>11017.85441797714</v>
       </c>
       <c r="I3">
-        <v>9.9753479302937542</v>
+        <v>17768.487543247538</v>
       </c>
       <c r="J3">
-        <v>2.233178716232409</v>
+        <v>1.4185187602157561</v>
       </c>
       <c r="K3">
-        <v>18.989501161932889</v>
+        <v>1.224798003861292</v>
       </c>
       <c r="L3">
-        <v>0.28699046494431529</v>
+        <v>0.737412726366513</v>
       </c>
       <c r="M3">
-        <v>6.5597004784897439E-2</v>
-      </c>
-      <c r="N3">
-        <v>0.53086058215761767</v>
-      </c>
-      <c r="O3">
-        <v>0.4857722424815889</v>
-      </c>
-      <c r="P3">
-        <v>0.1149809375008662</v>
-      </c>
-      <c r="Q3">
-        <v>0.99731430882431615</v>
-      </c>
-      <c r="R3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+        <v>2.102032312976192</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B4">
-        <v>64</v>
+        <v>13.17346639811938</v>
       </c>
       <c r="C4">
-        <v>13.17346639811938</v>
+        <v>12.93377186000111</v>
       </c>
       <c r="D4">
         <v>10.202260447115769</v>
@@ -742,54 +648,39 @@
         <v>15.306713940122849</v>
       </c>
       <c r="F4">
-        <v>3.0925769728628492</v>
+        <v>14024.878159447049</v>
       </c>
       <c r="G4">
-        <v>0.91650016750391894</v>
+        <v>14148.78346107383</v>
       </c>
       <c r="H4">
-        <v>5.9665144901869596</v>
+        <v>11035.099179225261</v>
       </c>
       <c r="I4">
-        <v>9.1598421134851762</v>
+        <v>17749.959014978591</v>
       </c>
       <c r="J4">
-        <v>3.001276662554393</v>
+        <v>1.2033094560899611</v>
       </c>
       <c r="K4">
-        <v>17.021682642136419</v>
+        <v>1.115219274432403</v>
       </c>
       <c r="L4">
-        <v>0.23905832573581731</v>
+        <v>0.74093762056533219</v>
       </c>
       <c r="M4">
-        <v>6.5069854831023372E-2</v>
-      </c>
-      <c r="N4">
-        <v>0.4526437597995403</v>
-      </c>
-      <c r="O4">
-        <v>0.51074519486719683</v>
-      </c>
-      <c r="P4">
-        <v>0.102619715941298</v>
-      </c>
-      <c r="Q4">
-        <v>1.135300467487278</v>
-      </c>
-      <c r="R4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+        <v>1.6659925072188499</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B5">
-        <v>67</v>
+        <v>-2.0977646948835389</v>
       </c>
       <c r="C5">
-        <v>-2.0977646948835389</v>
+        <v>-1.472321300172325</v>
       </c>
       <c r="D5">
         <v>-4.1805101316962068</v>
@@ -798,54 +689,39 @@
         <v>-0.96790092906397895</v>
       </c>
       <c r="F5">
-        <v>0.94385247299085628</v>
+        <v>2545.186408270808</v>
       </c>
       <c r="G5">
-        <v>0.23497297361922739</v>
+        <v>2162.4225845356459</v>
       </c>
       <c r="H5">
-        <v>2.245104512153318</v>
+        <v>1162.4177115871551</v>
       </c>
       <c r="I5">
-        <v>14.63931646774463</v>
+        <v>4006.6857154954878</v>
       </c>
       <c r="J5">
-        <v>4.1394702314119574</v>
+        <v>0.6261438466606728</v>
       </c>
       <c r="K5">
-        <v>25.1935548184812</v>
+        <v>0.53489118915438305</v>
       </c>
       <c r="L5">
-        <v>0.48990302687764459</v>
+        <v>8.5698262402222586E-2</v>
       </c>
       <c r="M5">
-        <v>0.1622975966758653</v>
-      </c>
-      <c r="N5">
-        <v>1.016948265503929</v>
-      </c>
-      <c r="O5">
-        <v>1.527169384018217</v>
-      </c>
-      <c r="P5">
-        <v>0.2446026026280482</v>
-      </c>
-      <c r="Q5">
-        <v>3.0789281096956098</v>
-      </c>
-      <c r="R5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+        <v>1.312045432651908</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B6">
-        <v>43</v>
+        <v>5.2039073665505864</v>
       </c>
       <c r="C6">
-        <v>5.2039073665505864</v>
+        <v>5.3420129792609652</v>
       </c>
       <c r="D6">
         <v>4.206301859210253</v>
@@ -854,54 +730,39 @@
         <v>5.8780580875312101</v>
       </c>
       <c r="F6">
-        <v>0.51058782399168412</v>
+        <v>701.39351154897622</v>
       </c>
       <c r="G6">
-        <v>0.15872163149105981</v>
+        <v>690.19420455362535</v>
       </c>
       <c r="H6">
-        <v>1.059256004864322</v>
+        <v>550.59515978627633</v>
       </c>
       <c r="I6">
-        <v>3.4173240357514731</v>
+        <v>869.76217100292104</v>
       </c>
       <c r="J6">
-        <v>0.97746012661432913</v>
+        <v>6.3452666948256358</v>
       </c>
       <c r="K6">
-        <v>7.885198171288974</v>
+        <v>5.9152840586880711</v>
       </c>
       <c r="L6">
-        <v>0.1039761684853666</v>
+        <v>1.4206362558345329</v>
       </c>
       <c r="M6">
-        <v>3.080854874072864E-2</v>
-      </c>
-      <c r="N6">
-        <v>0.2401369024916413</v>
-      </c>
-      <c r="O6">
-        <v>0.31356083237462939</v>
-      </c>
-      <c r="P6">
-        <v>8.6010905443233393E-2</v>
-      </c>
-      <c r="Q6">
-        <v>0.62549688644171286</v>
-      </c>
-      <c r="R6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+        <v>9.739023260119426</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B7">
-        <v>39</v>
+        <v>8.7198183198723953</v>
       </c>
       <c r="C7">
-        <v>8.7198183198723953</v>
+        <v>7.3883384358530524</v>
       </c>
       <c r="D7">
         <v>4.2479678389745779</v>
@@ -910,54 +771,39 @@
         <v>14.193357903815979</v>
       </c>
       <c r="F7">
-        <v>1.804642682338913</v>
+        <v>1054.3351067926999</v>
       </c>
       <c r="G7">
-        <v>0.36587450789617099</v>
+        <v>964.88322918517451</v>
       </c>
       <c r="H7">
-        <v>3.915364465831769</v>
+        <v>814.15500210164555</v>
       </c>
       <c r="I7">
-        <v>8.3469475261037029</v>
+        <v>1533.60455690349</v>
       </c>
       <c r="J7">
-        <v>2.5266151281069762</v>
+        <v>1.113868635439162</v>
       </c>
       <c r="K7">
-        <v>14.808767059195921</v>
+        <v>1.134666901528351</v>
       </c>
       <c r="L7">
-        <v>0.20351665897930049</v>
+        <v>0.44916459411811982</v>
       </c>
       <c r="M7">
-        <v>7.1662828543274021E-2</v>
-      </c>
-      <c r="N7">
-        <v>0.33395240502466927</v>
-      </c>
-      <c r="O7">
-        <v>0.29591704183928019</v>
-      </c>
-      <c r="P7">
-        <v>5.3463183747080242E-2</v>
-      </c>
-      <c r="Q7">
-        <v>0.49611246562692668</v>
-      </c>
-      <c r="R7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+        <v>1.5938837087670279</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B8">
-        <v>40</v>
+        <v>-16.888108964788991</v>
       </c>
       <c r="C8">
-        <v>-16.888108964788991</v>
+        <v>-16.4093027940275</v>
       </c>
       <c r="D8">
         <v>-20.715631144323279</v>
@@ -966,54 +812,39 @@
         <v>-14.04432133606001</v>
       </c>
       <c r="F8">
-        <v>2.3760602744363069</v>
+        <v>3248.7191180750569</v>
       </c>
       <c r="G8">
-        <v>0.36374367009877301</v>
+        <v>3100.6045923152528</v>
       </c>
       <c r="H8">
-        <v>4.8411666193079519</v>
+        <v>2177.4316287055308</v>
       </c>
       <c r="I8">
-        <v>3.322158141153372</v>
+        <v>4579.2454329904958</v>
       </c>
       <c r="J8">
-        <v>0.57801118536844975</v>
+        <v>5.1527506626399227</v>
       </c>
       <c r="K8">
-        <v>7.5098830059151078</v>
+        <v>3.000560810273845</v>
       </c>
       <c r="L8">
-        <v>0.1422054681848493</v>
+        <v>1.660254321366319</v>
       </c>
       <c r="M8">
-        <v>2.2176252763842011E-2</v>
-      </c>
-      <c r="N8">
-        <v>0.3012596068857703</v>
-      </c>
-      <c r="O8">
-        <v>0.27356376822082018</v>
-      </c>
-      <c r="P8">
-        <v>4.9207828687920868E-2</v>
-      </c>
-      <c r="Q8">
-        <v>0.52952785827401949</v>
-      </c>
-      <c r="R8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+        <v>11.02568817246045</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B9">
-        <v>32</v>
+        <v>-56.642077832557973</v>
       </c>
       <c r="C9">
-        <v>-56.642077832557973</v>
+        <v>-57.35807882810694</v>
       </c>
       <c r="D9">
         <v>-71.491168010467206</v>
@@ -1022,54 +853,39 @@
         <v>-40.445618244110321</v>
       </c>
       <c r="F9">
-        <v>14.571269687106581</v>
+        <v>53120.631759796743</v>
       </c>
       <c r="G9">
-        <v>5.4955227247252676</v>
+        <v>55447.102917117059</v>
       </c>
       <c r="H9">
-        <v>22.95931652166961</v>
+        <v>27625.406708987011</v>
       </c>
       <c r="I9">
-        <v>10.49350624672357</v>
+        <v>80021.002952324445</v>
       </c>
       <c r="J9">
-        <v>4.0581098334871388</v>
+        <v>1.015356861847925</v>
       </c>
       <c r="K9">
-        <v>16.793223353004059</v>
+        <v>1.002958705377639</v>
       </c>
       <c r="L9">
-        <v>0.25566404585039271</v>
+        <v>0.76489671435117257</v>
       </c>
       <c r="M9">
-        <v>9.1390896365951477E-2</v>
-      </c>
-      <c r="N9">
-        <v>0.4251695881080475</v>
-      </c>
-      <c r="O9">
-        <v>0.59607922363362909</v>
-      </c>
-      <c r="P9">
-        <v>0.23443624654991241</v>
-      </c>
-      <c r="Q9">
-        <v>1.094960480747232</v>
-      </c>
-      <c r="R9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+        <v>1.3475366168412559</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B10">
-        <v>29</v>
+        <v>18.86045661348783</v>
       </c>
       <c r="C10">
-        <v>18.86045661348783</v>
+        <v>18.933590796198231</v>
       </c>
       <c r="D10">
         <v>18.270209183294408</v>
@@ -1078,54 +894,39 @@
         <v>19.51797959576194</v>
       </c>
       <c r="F10">
-        <v>1.157829258569627</v>
+        <v>5957.1954765452456</v>
       </c>
       <c r="G10">
-        <v>0.4548273846678238</v>
+        <v>5981.3633822771862</v>
       </c>
       <c r="H10">
-        <v>1.926355910484745</v>
+        <v>5761.0909882017622</v>
       </c>
       <c r="I10">
-        <v>1.7947300422981201</v>
+        <v>6172.6642360712276</v>
       </c>
       <c r="J10">
-        <v>0.67882653159857809</v>
+        <v>1.051054369072852</v>
       </c>
       <c r="K10">
-        <v>2.9792964146261678</v>
+        <v>1.0511177970099641</v>
       </c>
       <c r="L10">
-        <v>6.1256469439296718E-2</v>
+        <v>0.95581549971840241</v>
       </c>
       <c r="M10">
-        <v>2.363990672685273E-2</v>
-      </c>
-      <c r="N10">
-        <v>0.1024519901963451</v>
-      </c>
-      <c r="O10">
-        <v>9.4293002019315897E-2</v>
-      </c>
-      <c r="P10">
-        <v>2.4314862314677749E-2</v>
-      </c>
-      <c r="Q10">
-        <v>0.1593430818887121</v>
-      </c>
-      <c r="R10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+        <v>1.1489722132115749</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B11">
-        <v>52</v>
+        <v>65.764013047921495</v>
       </c>
       <c r="C11">
-        <v>65.764013047921495</v>
+        <v>52.085050363026468</v>
       </c>
       <c r="D11">
         <v>42.618105276037419</v>
@@ -1134,54 +935,39 @@
         <v>106.5737840801379</v>
       </c>
       <c r="F11">
-        <v>18.213429421539349</v>
+        <v>75697.538547745906</v>
       </c>
       <c r="G11">
-        <v>8.143436079781404</v>
+        <v>69256.08085476869</v>
       </c>
       <c r="H11">
-        <v>26.927631045680972</v>
+        <v>55579.529071671772</v>
       </c>
       <c r="I11">
-        <v>11.670696729488521</v>
+        <v>107881.2653035032</v>
       </c>
       <c r="J11">
-        <v>5.3515152487060433</v>
+        <v>3.0592869156093832</v>
       </c>
       <c r="K11">
-        <v>18.788778373051631</v>
+        <v>3.0575281927781019</v>
       </c>
       <c r="L11">
-        <v>0.29344586707741482</v>
+        <v>1.204654717344765</v>
       </c>
       <c r="M11">
-        <v>0.14071286825461099</v>
-      </c>
-      <c r="N11">
-        <v>0.41264366681703452</v>
-      </c>
-      <c r="O11">
-        <v>0.60429594108930507</v>
-      </c>
-      <c r="P11">
-        <v>2.2750169953658309E-2</v>
-      </c>
-      <c r="Q11">
-        <v>1.239530390098748</v>
-      </c>
-      <c r="R11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+        <v>4.8137397820540446</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B12">
-        <v>41</v>
+        <v>4.9440846410675494</v>
       </c>
       <c r="C12">
-        <v>4.9440846410675494</v>
+        <v>4.615304027715287</v>
       </c>
       <c r="D12">
         <v>3.2941136772923829</v>
@@ -1190,54 +976,39 @@
         <v>7.4455800466796003</v>
       </c>
       <c r="F12">
-        <v>0.54215593846432064</v>
+        <v>5959.2503984721807</v>
       </c>
       <c r="G12">
-        <v>0.13697830814575951</v>
+        <v>5778.4675483450228</v>
       </c>
       <c r="H12">
-        <v>1.0633704352739071</v>
+        <v>4649.3923125418714</v>
       </c>
       <c r="I12">
-        <v>4.9088646762740984</v>
+        <v>8168.2060391751693</v>
       </c>
       <c r="J12">
-        <v>1.656155423769353</v>
+        <v>1.7909127472511861</v>
       </c>
       <c r="K12">
-        <v>9.2023253488597359</v>
+        <v>1.0554639231663681</v>
       </c>
       <c r="L12">
-        <v>0.1211214871869787</v>
+        <v>0.67987161797122142</v>
       </c>
       <c r="M12">
-        <v>3.7843758744248959E-2</v>
-      </c>
-      <c r="N12">
-        <v>0.25519947894571732</v>
-      </c>
-      <c r="O12">
-        <v>0.3338901113535237</v>
-      </c>
-      <c r="P12">
-        <v>7.7748971077489848E-2</v>
-      </c>
-      <c r="Q12">
-        <v>0.79320269007619437</v>
-      </c>
-      <c r="R12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+        <v>1.6847808892420559</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B13">
-        <v>36</v>
+        <v>-3.15959844925227</v>
       </c>
       <c r="C13">
-        <v>-3.15959844925227</v>
+        <v>-3.22551098976263</v>
       </c>
       <c r="D13">
         <v>-4.1468979691671519</v>
@@ -1246,54 +1017,39 @@
         <v>-1.965055156949554</v>
       </c>
       <c r="F13">
-        <v>1.039150950932842</v>
+        <v>556.30809304892671</v>
       </c>
       <c r="G13">
-        <v>0.21820985960453421</v>
+        <v>512.51859348135781</v>
       </c>
       <c r="H13">
-        <v>2.2174581637940269</v>
+        <v>371.74617339840438</v>
       </c>
       <c r="I13">
-        <v>10.043384128380669</v>
+        <v>791.12896906002095</v>
       </c>
       <c r="J13">
-        <v>1.900093371304203</v>
+        <v>0.99613239839191359</v>
       </c>
       <c r="K13">
-        <v>22.885937729760901</v>
+        <v>0.87413464003987218</v>
       </c>
       <c r="L13">
-        <v>0.38487783583613949</v>
+        <v>0.46850658174070708</v>
       </c>
       <c r="M13">
-        <v>6.1239321815827377E-2</v>
-      </c>
-      <c r="N13">
-        <v>0.98761467582252349</v>
-      </c>
-      <c r="O13">
-        <v>0.55100629022944214</v>
-      </c>
-      <c r="P13">
-        <v>0.19831608893499961</v>
-      </c>
-      <c r="Q13">
-        <v>1.017351194491269</v>
-      </c>
-      <c r="R13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+        <v>1.562170717042785</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B14">
-        <v>49</v>
+        <v>-4.0438074744874024</v>
       </c>
       <c r="C14">
-        <v>-4.0438074744874024</v>
+        <v>-3.7360903888733441</v>
       </c>
       <c r="D14">
         <v>-5.4747139890150107</v>
@@ -1302,54 +1058,39 @@
         <v>-2.6964208457095649</v>
       </c>
       <c r="F14">
-        <v>1.1909276327946949</v>
+        <v>1929.7038762917541</v>
       </c>
       <c r="G14">
-        <v>0.31429592858137489</v>
+        <v>1579.2353766487049</v>
       </c>
       <c r="H14">
-        <v>1.5960465957018259</v>
+        <v>995.54693512784991</v>
       </c>
       <c r="I14">
-        <v>10.51811708833381</v>
+        <v>2768.0569890092611</v>
       </c>
       <c r="J14">
-        <v>2.8299876246908791</v>
+        <v>0.90173809876126365</v>
       </c>
       <c r="K14">
-        <v>18.565783002550909</v>
+        <v>0.89913189501831925</v>
       </c>
       <c r="L14">
-        <v>0.29516499612325459</v>
+        <v>0.31576311058554551</v>
       </c>
       <c r="M14">
-        <v>8.0615183198875173E-2</v>
-      </c>
-      <c r="N14">
-        <v>0.52599787748634919</v>
-      </c>
-      <c r="O14">
-        <v>1.112917962525303</v>
-      </c>
-      <c r="P14">
-        <v>0.48686857375608372</v>
-      </c>
-      <c r="Q14">
-        <v>1.811042389707239</v>
-      </c>
-      <c r="R14" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+        <v>1.4188969866406751</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B15">
-        <v>29</v>
+        <v>21.27815559165224</v>
       </c>
       <c r="C15">
-        <v>21.27815559165224</v>
+        <v>21.59952673380586</v>
       </c>
       <c r="D15">
         <v>17.37104652669575</v>
@@ -1358,54 +1099,39 @@
         <v>24.660635827057892</v>
       </c>
       <c r="F15">
-        <v>4.658284702822999</v>
+        <v>6373.8164358308368</v>
       </c>
       <c r="G15">
-        <v>1.947270560635378</v>
+        <v>6005.0951474659823</v>
       </c>
       <c r="H15">
-        <v>8.1722078362073525</v>
+        <v>5040.4813764169876</v>
       </c>
       <c r="I15">
-        <v>6.4116094328469746</v>
+        <v>8406.7222024257044</v>
       </c>
       <c r="J15">
-        <v>2.7205287896557868</v>
+        <v>1.5797780343547581</v>
       </c>
       <c r="K15">
-        <v>10.911564292373839</v>
+        <v>1.5351025415085191</v>
       </c>
       <c r="L15">
-        <v>0.22199200033265121</v>
+        <v>1.2825652008716759</v>
       </c>
       <c r="M15">
-        <v>8.9976322554277954E-2</v>
-      </c>
-      <c r="N15">
-        <v>0.37462463379601868</v>
-      </c>
-      <c r="O15">
-        <v>1.224398905381276</v>
-      </c>
-      <c r="P15">
-        <v>0.52040009800228104</v>
-      </c>
-      <c r="Q15">
-        <v>1.9442067793232849</v>
-      </c>
-      <c r="R15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+        <v>2.0136135066667178</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B16">
-        <v>32</v>
+        <v>-3.177143017947158</v>
       </c>
       <c r="C16">
-        <v>-3.177143017947158</v>
+        <v>-2.6734115964111029</v>
       </c>
       <c r="D16">
         <v>-5.2652427175711152</v>
@@ -1414,54 +1140,39 @@
         <v>-1.444732958393129</v>
       </c>
       <c r="F16">
-        <v>1.0115997851876379</v>
+        <v>17820.263903129409</v>
       </c>
       <c r="G16">
-        <v>0.1874644565947059</v>
+        <v>14528.259690430499</v>
       </c>
       <c r="H16">
-        <v>1.980229471566632</v>
+        <v>8898.7365694270047</v>
       </c>
       <c r="I16">
-        <v>7.4576621852468072</v>
+        <v>26650.07447742781</v>
       </c>
       <c r="J16">
-        <v>2.0277799183062988</v>
+        <v>0.14446771033700989</v>
       </c>
       <c r="K16">
-        <v>13.07740483645472</v>
+        <v>9.3653751916399491E-2</v>
       </c>
       <c r="L16">
-        <v>0.30567928544613848</v>
+        <v>1.9806127251702908E-2</v>
       </c>
       <c r="M16">
-        <v>0.13658902210891999</v>
-      </c>
-      <c r="N16">
-        <v>0.4784973846313727</v>
-      </c>
-      <c r="O16">
-        <v>0.51746354824092156</v>
-      </c>
-      <c r="P16">
-        <v>6.3628306895300774E-2</v>
-      </c>
-      <c r="Q16">
-        <v>1.1040377162881869</v>
-      </c>
-      <c r="R16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0.2388338407587908</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B17">
-        <v>26</v>
+        <v>-4.8447728495190914</v>
       </c>
       <c r="C17">
-        <v>-4.8447728495190914</v>
+        <v>-4.4153069054052798</v>
       </c>
       <c r="D17">
         <v>-5.2976000107742669</v>
@@ -1470,54 +1181,39 @@
         <v>-3.953375893529762</v>
       </c>
       <c r="F17">
-        <v>0.90366119352192087</v>
+        <v>1634.926285286341</v>
       </c>
       <c r="G17">
-        <v>0.51221990630227632</v>
+        <v>1489.8104330536121</v>
       </c>
       <c r="H17">
-        <v>1.269203992849959</v>
+        <v>1340.881316356285</v>
       </c>
       <c r="I17">
-        <v>5.585553226915172</v>
+        <v>1749.1955536183459</v>
       </c>
       <c r="J17">
-        <v>3.1465450013032128</v>
+        <v>2.0423126095485138</v>
       </c>
       <c r="K17">
-        <v>8.1936703595419971</v>
+        <v>2.1463957415343069</v>
       </c>
       <c r="L17">
-        <v>0.1938266431084022</v>
+        <v>1.4919862418820431</v>
       </c>
       <c r="M17">
-        <v>0.1127773535668103</v>
-      </c>
-      <c r="N17">
-        <v>0.27775594933166819</v>
-      </c>
-      <c r="O17">
-        <v>0.35427841633032392</v>
-      </c>
-      <c r="P17">
-        <v>0.15836367597899481</v>
-      </c>
-      <c r="Q17">
-        <v>0.55462246816310323</v>
-      </c>
-      <c r="R17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+        <v>2.5601858432737572</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B18">
-        <v>57</v>
+        <v>-3.1870294979112388</v>
       </c>
       <c r="C18">
-        <v>-3.1870294979112388</v>
+        <v>-2.81587283716873</v>
       </c>
       <c r="D18">
         <v>-4.6113164096759878</v>
@@ -1526,54 +1222,39 @@
         <v>-2.288447068500036</v>
       </c>
       <c r="F18">
-        <v>0.75181295399350179</v>
+        <v>3306.0146933649471</v>
       </c>
       <c r="G18">
-        <v>0.22113005779326311</v>
+        <v>3321.171698756134</v>
       </c>
       <c r="H18">
-        <v>1.3633421885371479</v>
+        <v>2077.9980528837568</v>
       </c>
       <c r="I18">
-        <v>8.5117159433059424</v>
+        <v>4651.3867059341092</v>
       </c>
       <c r="J18">
-        <v>2.061047260518543</v>
+        <v>0.82274328556738874</v>
       </c>
       <c r="K18">
-        <v>14.35918111163673</v>
+        <v>0.76062148583243983</v>
       </c>
       <c r="L18">
-        <v>0.23739049528539319</v>
+        <v>0.51528098113760856</v>
       </c>
       <c r="M18">
-        <v>5.2273126197715951E-2</v>
-      </c>
-      <c r="N18">
-        <v>0.43897925759755319</v>
-      </c>
-      <c r="O18">
-        <v>0.55562874890838954</v>
-      </c>
-      <c r="P18">
-        <v>0.21297836818162169</v>
-      </c>
-      <c r="Q18">
-        <v>1.043734835050149</v>
-      </c>
-      <c r="R18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+        <v>1.2906995214972641</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B19">
-        <v>44</v>
+        <v>-18.015795613089779</v>
       </c>
       <c r="C19">
-        <v>-18.015795613089779</v>
+        <v>-17.209004363820281</v>
       </c>
       <c r="D19">
         <v>-21.719204686065261</v>
@@ -1582,54 +1263,39 @@
         <v>-14.22774559383563</v>
       </c>
       <c r="F19">
-        <v>2.7680997014161579</v>
+        <v>22159.481821891532</v>
       </c>
       <c r="G19">
-        <v>0.91544587803285027</v>
+        <v>25063.19665315792</v>
       </c>
       <c r="H19">
-        <v>4.9812845972072308</v>
+        <v>13049.269844701579</v>
       </c>
       <c r="I19">
-        <v>6.6641071415179249</v>
+        <v>29797.16883596166</v>
       </c>
       <c r="J19">
-        <v>2.4913310909437132</v>
+        <v>1.47399216162304</v>
       </c>
       <c r="K19">
-        <v>13.021430273067139</v>
+        <v>1.3297714145568089</v>
       </c>
       <c r="L19">
-        <v>0.16166356796625631</v>
+        <v>0.84281484025591369</v>
       </c>
       <c r="M19">
-        <v>4.9922490036548348E-2</v>
-      </c>
-      <c r="N19">
-        <v>0.30856172802798082</v>
-      </c>
-      <c r="O19">
-        <v>0.8950292705901941</v>
-      </c>
-      <c r="P19">
-        <v>0.21754062173211761</v>
-      </c>
-      <c r="Q19">
-        <v>1.752653077395357</v>
-      </c>
-      <c r="R19" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+        <v>2.616911149939591</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B20">
-        <v>39</v>
+        <v>-14.19900789319794</v>
       </c>
       <c r="C20">
-        <v>-14.19900789319794</v>
+        <v>-15.1114763548492</v>
       </c>
       <c r="D20">
         <v>-18.859224662750169</v>
@@ -1638,54 +1304,39 @@
         <v>-8.1463204977413657</v>
       </c>
       <c r="F20">
-        <v>1.711661596994589</v>
+        <v>3563.4225879590781</v>
       </c>
       <c r="G20">
-        <v>0.67146857720631636</v>
+        <v>3611.1746498707889</v>
       </c>
       <c r="H20">
-        <v>3.352182815140643</v>
+        <v>1725.0181264514781</v>
       </c>
       <c r="I20">
-        <v>5.4679460433557114</v>
+        <v>5619.0734287709338</v>
       </c>
       <c r="J20">
-        <v>1.7096848311112709</v>
+        <v>0.96420618048119389</v>
       </c>
       <c r="K20">
-        <v>10.705487711724709</v>
+        <v>0.66100850190459004</v>
       </c>
       <c r="L20">
-        <v>0.1202036143702583</v>
+        <v>0.16349187815266239</v>
       </c>
       <c r="M20">
-        <v>5.3274908894137253E-2</v>
-      </c>
-      <c r="N20">
-        <v>0.21504300359527159</v>
-      </c>
-      <c r="O20">
-        <v>0.44288628139661201</v>
-      </c>
-      <c r="P20">
-        <v>0.15396478715866449</v>
-      </c>
-      <c r="Q20">
-        <v>0.76773519182003014</v>
-      </c>
-      <c r="R20" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+        <v>1.7677292575989569</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B21">
-        <v>39</v>
+        <v>-3.3482265048236108</v>
       </c>
       <c r="C21">
-        <v>-3.3482265048236108</v>
+        <v>-3.3569403660065178</v>
       </c>
       <c r="D21">
         <v>-4.7801120116736762</v>
@@ -1694,54 +1345,39 @@
         <v>-1.919504771788455</v>
       </c>
       <c r="F21">
-        <v>1.4095604490474669</v>
+        <v>13098.97936193494</v>
       </c>
       <c r="G21">
-        <v>0.51143380691135154</v>
+        <v>12897.560036084449</v>
       </c>
       <c r="H21">
-        <v>2.0597737000795169</v>
+        <v>7935.1843988356586</v>
       </c>
       <c r="I21">
-        <v>15.32585028329636</v>
+        <v>18915.91835501973</v>
       </c>
       <c r="J21">
-        <v>6.6714901729963696</v>
+        <v>4.1639950783638302E-2</v>
       </c>
       <c r="K21">
-        <v>26.442417900639079</v>
+        <v>2.19110076258138E-2</v>
       </c>
       <c r="L21">
-        <v>0.45601558603186287</v>
+        <v>9.6551067533213759E-3</v>
       </c>
       <c r="M21">
-        <v>0.20464940015564911</v>
-      </c>
-      <c r="N21">
-        <v>0.80570231835172423</v>
-      </c>
-      <c r="O21">
-        <v>0.6475499894619211</v>
-      </c>
-      <c r="P21">
-        <v>0.21192399742820409</v>
-      </c>
-      <c r="Q21">
-        <v>1.2148624171823239</v>
-      </c>
-      <c r="R21" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0.10164091787851209</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B22">
-        <v>29</v>
+        <v>-0.90783789449131103</v>
       </c>
       <c r="C22">
-        <v>-0.90783789449131103</v>
+        <v>-0.80991784813014289</v>
       </c>
       <c r="D22">
         <v>-1.557215941153719</v>
@@ -1750,54 +1386,39 @@
         <v>-0.56633642941198525</v>
       </c>
       <c r="F22">
-        <v>0.31228739243297632</v>
+        <v>191.13389735152151</v>
       </c>
       <c r="G22">
-        <v>0.14334619313714411</v>
+        <v>173.85498678749869</v>
       </c>
       <c r="H22">
-        <v>0.44644635375843678</v>
+        <v>121.8949797802083</v>
       </c>
       <c r="I22">
-        <v>13.26623829941674</v>
+        <v>280.10083653931741</v>
       </c>
       <c r="J22">
-        <v>3.8773846630640381</v>
+        <v>0.23634580176068509</v>
       </c>
       <c r="K22">
-        <v>20.82327707437662</v>
+        <v>0.19779462314358759</v>
       </c>
       <c r="L22">
-        <v>0.37568847678581641</v>
+        <v>6.4774845288474006E-2</v>
       </c>
       <c r="M22">
-        <v>0.19602759663190519</v>
-      </c>
-      <c r="N22">
-        <v>0.67453810273627945</v>
-      </c>
-      <c r="O22">
-        <v>1.0710716724933289</v>
-      </c>
-      <c r="P22">
-        <v>0.31289112508740491</v>
-      </c>
-      <c r="Q22">
-        <v>2.17795111314532</v>
-      </c>
-      <c r="R22" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0.43689645877803968</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B23">
-        <v>45</v>
+        <v>-1.563089529147526</v>
       </c>
       <c r="C23">
-        <v>-1.563089529147526</v>
+        <v>-0.96929338881346239</v>
       </c>
       <c r="D23">
         <v>-3.4741858795251348</v>
@@ -1806,54 +1427,39 @@
         <v>-0.52150200812600345</v>
       </c>
       <c r="F23">
-        <v>1.0614972388457851</v>
+        <v>1451.26867295333</v>
       </c>
       <c r="G23">
-        <v>0.18951767029819161</v>
+        <v>870.40916005466681</v>
       </c>
       <c r="H23">
-        <v>1.672848316590084</v>
+        <v>415.20767248964859</v>
       </c>
       <c r="I23">
-        <v>18.780794366901741</v>
+        <v>2750.790226297489</v>
       </c>
       <c r="J23">
-        <v>6.5312348908865276</v>
+        <v>0.22423295015559391</v>
       </c>
       <c r="K23">
-        <v>37.915964042460793</v>
+        <v>0.17014786012474381</v>
       </c>
       <c r="L23">
-        <v>0.72013276956123984</v>
+        <v>1.6765148047604719E-2</v>
       </c>
       <c r="M23">
-        <v>0.21334372274116789</v>
-      </c>
-      <c r="N23">
-        <v>1.4711970374462651</v>
-      </c>
-      <c r="O23">
-        <v>1.653038203610995</v>
-      </c>
-      <c r="P23">
-        <v>0.4812003586440296</v>
-      </c>
-      <c r="Q23">
-        <v>4.3682948073213561</v>
-      </c>
-      <c r="R23" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0.42639226419930892</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B24">
-        <v>38</v>
+        <v>-3.5326280293426291</v>
       </c>
       <c r="C24">
-        <v>-3.5326280293426291</v>
+        <v>-2.8722360695883009</v>
       </c>
       <c r="D24">
         <v>-5.1080339909529249</v>
@@ -1862,54 +1468,39 @@
         <v>-2.0781700594100569</v>
       </c>
       <c r="F24">
-        <v>1.255355682549719</v>
+        <v>991.62865920909655</v>
       </c>
       <c r="G24">
-        <v>0.32846269306881309</v>
+        <v>865.31194236150736</v>
       </c>
       <c r="H24">
-        <v>2.1091264664887488</v>
+        <v>607.87846301611955</v>
       </c>
       <c r="I24">
-        <v>13.62853186649315</v>
+        <v>1350.9465665115561</v>
       </c>
       <c r="J24">
-        <v>3.9720806300777349</v>
+        <v>0.28810285389591622</v>
       </c>
       <c r="K24">
-        <v>23.198320924009121</v>
+        <v>0.25661683284476339</v>
       </c>
       <c r="L24">
-        <v>0.38334799154844917</v>
+        <v>0.1130148283647493</v>
       </c>
       <c r="M24">
-        <v>9.5949473828543644E-2</v>
-      </c>
-      <c r="N24">
-        <v>0.66946138787735032</v>
-      </c>
-      <c r="O24">
-        <v>0.53665723812924282</v>
-      </c>
-      <c r="P24">
-        <v>0.19893575164154831</v>
-      </c>
-      <c r="Q24">
-        <v>0.91807097956407446</v>
-      </c>
-      <c r="R24" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0.4970081989657813</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B25">
-        <v>52</v>
+        <v>2.4354625535139451</v>
       </c>
       <c r="C25">
-        <v>2.4354625535139451</v>
+        <v>2.354113464272463</v>
       </c>
       <c r="D25">
         <v>1.5379071732068581</v>
@@ -1918,43 +1509,28 @@
         <v>3.3550687537992618</v>
       </c>
       <c r="F25">
-        <v>0.79454292274974569</v>
+        <v>3853.0208081997639</v>
       </c>
       <c r="G25">
-        <v>0.29814601625279891</v>
+        <v>3420.958695743077</v>
       </c>
       <c r="H25">
-        <v>1.4067970196183499</v>
+        <v>2191.770334479439</v>
       </c>
       <c r="I25">
-        <v>10.44333606658375</v>
+        <v>6546.9377234950798</v>
       </c>
       <c r="J25">
-        <v>4.447562039115236</v>
+        <v>5.3279735505710173</v>
       </c>
       <c r="K25">
-        <v>18.67410973968196</v>
+        <v>4.5070343707107661</v>
       </c>
       <c r="L25">
-        <v>0.32413902901101982</v>
+        <v>1.810293347382016</v>
       </c>
       <c r="M25">
-        <v>0.14856908109048289</v>
-      </c>
-      <c r="N25">
-        <v>0.54942514311452373</v>
-      </c>
-      <c r="O25">
-        <v>1.1422514588380941</v>
-      </c>
-      <c r="P25">
-        <v>0.40649844033425681</v>
-      </c>
-      <c r="Q25">
-        <v>2.125781068702183</v>
-      </c>
-      <c r="R25" t="s">
-        <v>22</v>
+        <v>9.3950550797150107</v>
       </c>
     </row>
   </sheetData>

--- a/All data/results_publication_summary.xlsx
+++ b/All data/results_publication_summary.xlsx
@@ -1,26 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/44e2464d2a9165ff/Postdoc/2024 Plastic-detection/Plastic_tracker_codes/writing/submissions SciAdv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{FABD14B2-83CE-49FE-812C-ED495E223DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C92241C8-D59C-42FB-A0A6-EF7CA2ACD66A}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{FABD14B2-83CE-49FE-812C-ED495E223DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3EBCC48-1C2C-5048-8883-FC8D7A241F34}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -30,18 +25,6 @@
     <t>Common name</t>
   </si>
   <si>
-    <t>vz_mean_mean</t>
-  </si>
-  <si>
-    <t>vz_mean_median</t>
-  </si>
-  <si>
-    <t>vz_mean_p10</t>
-  </si>
-  <si>
-    <t>vz_mean_p90</t>
-  </si>
-  <si>
     <t>Re_mean</t>
   </si>
   <si>
@@ -136,6 +119,18 @@
   </si>
   <si>
     <t>Wet wipes</t>
+  </si>
+  <si>
+    <t>w_mean cm/s</t>
+  </si>
+  <si>
+    <t>w_median cm/s</t>
+  </si>
+  <si>
+    <t>w_p10 cm/s</t>
+  </si>
+  <si>
+    <t>w_p90 cm/s</t>
   </si>
 </sst>
 </file>
@@ -154,6 +149,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -211,6 +207,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -499,59 +499,59 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="13" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>13</v>
       </c>
       <c r="B2">
         <v>8.4702712528530419</v>
@@ -590,9 +590,9 @@
         <v>2.306799862533087</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>8.3186142931652558</v>
@@ -631,9 +631,9 @@
         <v>2.102032312976192</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>13.17346639811938</v>
@@ -672,9 +672,9 @@
         <v>1.6659925072188499</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B5">
         <v>-2.0977646948835389</v>
@@ -713,9 +713,9 @@
         <v>1.312045432651908</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B6">
         <v>5.2039073665505864</v>
@@ -754,9 +754,9 @@
         <v>9.739023260119426</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B7">
         <v>8.7198183198723953</v>
@@ -795,9 +795,9 @@
         <v>1.5938837087670279</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B8">
         <v>-16.888108964788991</v>
@@ -836,9 +836,9 @@
         <v>11.02568817246045</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B9">
         <v>-56.642077832557973</v>
@@ -877,9 +877,9 @@
         <v>1.3475366168412559</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B10">
         <v>18.86045661348783</v>
@@ -918,9 +918,9 @@
         <v>1.1489722132115749</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B11">
         <v>65.764013047921495</v>
@@ -959,9 +959,9 @@
         <v>4.8137397820540446</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B12">
         <v>4.9440846410675494</v>
@@ -1000,9 +1000,9 @@
         <v>1.6847808892420559</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B13">
         <v>-3.15959844925227</v>
@@ -1041,9 +1041,9 @@
         <v>1.562170717042785</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B14">
         <v>-4.0438074744874024</v>
@@ -1082,9 +1082,9 @@
         <v>1.4188969866406751</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B15">
         <v>21.27815559165224</v>
@@ -1123,9 +1123,9 @@
         <v>2.0136135066667178</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B16">
         <v>-3.177143017947158</v>
@@ -1164,9 +1164,9 @@
         <v>0.2388338407587908</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B17">
         <v>-4.8447728495190914</v>
@@ -1205,9 +1205,9 @@
         <v>2.5601858432737572</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B18">
         <v>-3.1870294979112388</v>
@@ -1246,9 +1246,9 @@
         <v>1.2906995214972641</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B19">
         <v>-18.015795613089779</v>
@@ -1287,9 +1287,9 @@
         <v>2.616911149939591</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B20">
         <v>-14.19900789319794</v>
@@ -1328,9 +1328,9 @@
         <v>1.7677292575989569</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B21">
         <v>-3.3482265048236108</v>
@@ -1369,9 +1369,9 @@
         <v>0.10164091787851209</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B22">
         <v>-0.90783789449131103</v>
@@ -1410,9 +1410,9 @@
         <v>0.43689645877803968</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B23">
         <v>-1.563089529147526</v>
@@ -1451,9 +1451,9 @@
         <v>0.42639226419930892</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B24">
         <v>-3.5326280293426291</v>
@@ -1492,9 +1492,9 @@
         <v>0.4970081989657813</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B25">
         <v>2.4354625535139451</v>
